--- a/output/Book1-translated.xlsx
+++ b/output/Book1-translated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duyvk\Downloads\TranslateDocument\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415BD3EA-E42B-4C79-B00B-0669E811730F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B82C0DF-A298-4316-AD7A-5A7C5F5C4735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{0D88EB89-2951-45B2-9874-0DD5662C534B}"/>
+    <workbookView xWindow="3072" yWindow="3072" windowWidth="17280" windowHeight="9420" xr2:uid="{0D88EB89-2951-45B2-9874-0DD5662C534B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
     <t>【Tổng quan】</t>
   </si>
   <si>
-    <t>Muốn xác thực đồng thời buổi biểu diễn của nhiều người dùng (người dùng A, người dùng B) bằng ứng dụng resQ.</t>
+    <t>Muốn xác thực đồng thời các buổi biểu diễn của nhiều người dùng (người dùng A, người dùng B) bằng ứng dụng resQ.</t>
   </si>
   <si>
     <t>【Bối cảnh】</t>
@@ -87,13 +87,13 @@
     <t>Nhiều người dùng (người dùng A, người dùng B) đang bán vé cho cùng một buổi biểu diễn trên Gettii với phương thức nhận vé là "resQ".</t>
   </si>
   <si>
-    <t>Trong trường hợp xác thực QR cho buổi biểu diễn trên, hiện tại cần chuẩn bị các thiết bị đầu vào chuyên dụng riêng cho người mua là người dùng A và người mua là người dùng B.</t>
-  </si>
-  <si>
-    <t>Tuy nhiên, người mua không thể xác định nên vào từ cổng nào chỉ bằng mã QR mang theo khi đến, dẫn đến tình trạng hỗn loạn ở cổng vào.</t>
-  </si>
-  <si>
-    <t>Để giải quyết vấn đề này, chúng tôi muốn có thể xác thực QR đồng thời buổi biểu diễn của nhiều người dùng trên một thiết bị resQ.</t>
+    <t>Trong trường hợp xác thực QR cho các buổi biểu diễn trên, hiện tại cần chuẩn bị các thiết bị đầu cuối chuyên dụng cho từng người dùng, một cho người mua là người dùng A và một cho người mua là người dùng B.</t>
+  </si>
+  <si>
+    <t>Tuy nhiên, người mua không thể xác định nên vào từ cổng nào chỉ bằng mã QR mang theo khi đến, gây ra sự nhầm lẫn ở cổng vào.</t>
+  </si>
+  <si>
+    <t>Để giải quyết vấn đề này, chúng tôi muốn có thể xác thực QR đồng thời các buổi biểu diễn của nhiều người dùng trên một thiết bị đầu cuối resQ.</t>
   </si>
   <si>
     <t>【Tổng quan về sửa đổi】</t>
@@ -105,16 +105,16 @@
     <t>Gettii quản lý APL</t>
   </si>
   <si>
-    <t>Phát hành số PIN duy nhất để xác định buổi biểu diễn (ngày biểu diễn, giờ bắt đầu) được xác thực bằng ứng dụng resQ</t>
+    <t>Phát hành mã PIN duy nhất để xác định buổi biểu diễn (ngày biểu diễn, thời gian bắt đầu) được xác thực bằng ứng dụng resQ</t>
   </si>
   <si>
     <t>resQ quản lý WEB</t>
   </si>
   <si>
-    <t>Liên kết số PIN đã phát hành với buổi biểu diễn được xác thực bằng ứng dụng resQ</t>
-  </si>
-  <si>
-    <t>(TODO) Trong trường hợp không kịp triển khai resQ quản lý WEB, vận hành bằng cách nhập dữ liệu thủ công vào DB</t>
+    <t>Liên kết mã PIN đã phát hành với buổi biểu diễn được xác thực bằng ứng dụng resQ</t>
+  </si>
+  <si>
+    <t>(TODO) Trong trường hợp không kịp triển khai resQ quản lý WEB, hãy nhập dữ liệu thủ công vào DB để vận hành</t>
   </si>
   <si>
     <t>Không thể liên kết vé chính và vé phụ</t>
@@ -123,31 +123,31 @@
     <t>Ứng dụng xác thực resQ</t>
   </si>
   <si>
-    <t>Có thể xác thực buổi biểu diễn được liên kết bằng số PIN khi xác thực trực tuyến</t>
-  </si>
-  <si>
-    <t>Có thể tải xuống buổi biểu diễn được liên kết bằng số PIN khi tải xuống dữ liệu ngoại tuyến</t>
-  </si>
-  <si>
-    <t>Có thể xác thực buổi biểu diễn được liên kết bằng số PIN khi xác thực ngoại tuyến</t>
-  </si>
-  <si>
-    <t>Khi tải lên dữ liệu ngoại tuyến, cập nhật buổi biểu diễn được liên kết bằng số PIN thành đã đến</t>
-  </si>
-  <si>
-    <t>Có thể xác thực buổi biểu diễn được liên kết bằng số PIN khi xác thực ở chế độ lỗi</t>
-  </si>
-  <si>
-    <t>Khi tải lên dữ liệu ngoại tuyến (dữ liệu xác thực chế độ lỗi), cập nhật buổi biểu diễn được liên kết bằng số PIN thành đã đến</t>
-  </si>
-  <si>
-    <t>Khi tải lên dữ liệu lỗi, cập nhật thông tin lỗi của buổi biểu diễn được liên kết bằng số PIN</t>
-  </si>
-  <si>
-    <t>Có thể xác thực buổi biểu diễn được liên kết bằng số PIN khi xác thực ở chế độ pre-run</t>
-  </si>
-  <si>
-    <t>Thông tin người vào cửa hiển thị tổng giá trị của buổi biểu diễn thông thường và buổi biểu diễn được liên kết bằng số PIN.</t>
+    <t>Có thể xác thực các buổi biểu diễn được liên kết bằng mã PIN khi xác thực trực tuyến</t>
+  </si>
+  <si>
+    <t>Có thể tải xuống các buổi biểu diễn được liên kết bằng mã PIN khi tải xuống dữ liệu ngoại tuyến</t>
+  </si>
+  <si>
+    <t>Có thể xác thực các buổi biểu diễn được liên kết bằng mã PIN khi xác thực ngoại tuyến</t>
+  </si>
+  <si>
+    <t>Khi tải lên dữ liệu ngoại tuyến, hãy cập nhật các buổi biểu diễn được liên kết bằng mã PIN thành đã đến</t>
+  </si>
+  <si>
+    <t>Có thể xác thực các buổi biểu diễn được liên kết bằng mã PIN khi xác thực ở chế độ lỗi</t>
+  </si>
+  <si>
+    <t>Khi tải lên dữ liệu ngoại tuyến (dữ liệu xác thực chế độ lỗi), hãy cập nhật các buổi biểu diễn được liên kết bằng mã PIN thành đã đến</t>
+  </si>
+  <si>
+    <t>Khi tải lên dữ liệu lỗi, hãy cập nhật thông tin lỗi của các buổi biểu diễn được liên kết bằng mã PIN</t>
+  </si>
+  <si>
+    <t>Có thể xác thực các buổi biểu diễn được liên kết bằng mã PIN khi xác thực ở chế độ pre-run</t>
+  </si>
+  <si>
+    <t>Thông tin người vào cửa hiển thị tổng giá trị của các buổi biểu diễn thông thường và các buổi biểu diễn được liên kết bằng mã PIN.</t>
   </si>
   <si>
     <t>(TODO) Chi tiết sẽ được hiển thị trên resQ quản lý WEB. Dự kiến triển khai lần sau</t>
